--- a/Lead Sheet.xlsx
+++ b/Lead Sheet.xlsx
@@ -1893,7 +1893,7 @@
         <v>https://www.linkedin.com/feed/</v>
       </c>
       <c r="L44" t="str">
-        <v>New</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="45">
